--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T17:19:03+00:00</t>
+    <t>2023-05-05T18:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:11+00:00</t>
+    <t>2023-05-05T18:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2814,7 +2814,7 @@
         <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>80</v>
@@ -2931,7 +2931,7 @@
         <v>87</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>80</v>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:45:12+00:00</t>
+    <t>2023-05-05T19:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:07+00:00</t>
+    <t>2023-05-05T19:04:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:40+00:00</t>
+    <t>2023-05-05T20:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,7 +455,7 @@
     <t>PAM</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/patient-age-days}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/patient-age-months}
 </t>
   </si>
   <si>
@@ -1708,7 +1708,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.11328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="80.97265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:22+00:00</t>
+    <t>2023-05-05T20:15:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:42+00:00</t>
+    <t>2023-05-05T20:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:19+00:00</t>
+    <t>2023-05-05T20:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:46+00:00</t>
+    <t>2023-05-05T20:33:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:33:04+00:00</t>
+    <t>2023-05-05T20:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:39:09+00:00</t>
+    <t>2023-05-05T20:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
